--- a/output/peer_comparison.xlsx
+++ b/output/peer_comparison.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-27 11:12</t>
+          <t>Generated: 2026-08-20 10:44</t>
         </is>
       </c>
     </row>
